--- a/data/trans_camb/IP26C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,96</t>
+          <t>-7,51; 5,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 0,27</t>
+          <t>-12,03; -0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 7,07</t>
+          <t>-6,43; 6,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 7,6</t>
+          <t>-3,63; 7,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 4,11</t>
+          <t>-6,07; 4,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 11,75</t>
+          <t>-2,58; 11,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,72</t>
+          <t>-3,78; 4,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,3</t>
+          <t>-7,54; 0,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 7,18</t>
+          <t>-2,66; 7,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 71,68</t>
+          <t>-52,18; 63,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 10,87</t>
+          <t>-77,42; 9,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 77,12</t>
+          <t>-43,64; 75,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 118,14</t>
+          <t>-31,57; 102,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,7; 68,51</t>
+          <t>-51,57; 63,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 165,88</t>
+          <t>-23,95; 162,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 55,86</t>
+          <t>-30,56; 58,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 6,63</t>
+          <t>-59,77; 4,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 82,96</t>
+          <t>-20,03; 92,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -0,91</t>
+          <t>-11,11; -1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -0,31</t>
+          <t>-10,64; -0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 3,25</t>
+          <t>-7,87; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,66</t>
+          <t>-3,09; 6,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,21</t>
+          <t>-6,03; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,72</t>
+          <t>-1,91; 8,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1,4</t>
+          <t>-5,04; 1,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -0,28</t>
+          <t>-6,68; -0,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,04</t>
+          <t>-3,34; 4,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,77; -5,25</t>
+          <t>-65,19; -7,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,25; -0,8</t>
+          <t>-62,71; -5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 28,43</t>
+          <t>-47,18; 26,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 85,49</t>
+          <t>-25,6; 81,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 42,74</t>
+          <t>-48,22; 35,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 95,98</t>
+          <t>-16,19; 107,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 13,81</t>
+          <t>-37,02; 12,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,91; -1,4</t>
+          <t>-48,75; -2,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 39,5</t>
+          <t>-24,11; 41,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,36</t>
+          <t>-5,51; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 8,55</t>
+          <t>-1,72; 9,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 2,47</t>
+          <t>-7,13; 2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 3,86</t>
+          <t>-7,37; 3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,51</t>
+          <t>-6,55; 5,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 0,35</t>
+          <t>-10,28; -0,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,66</t>
+          <t>-4,74; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,54</t>
+          <t>-2,6; 5,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -0,61</t>
+          <t>-7,51; -0,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 75,37</t>
+          <t>-51,9; 69,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 150,27</t>
+          <t>-18,45; 154,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,11; 42,9</t>
+          <t>-65,66; 44,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 50,63</t>
+          <t>-52,23; 47,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 79,33</t>
+          <t>-50,25; 66,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,19; 8,62</t>
+          <t>-74,69; -0,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 35,1</t>
+          <t>-40,11; 31,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 73,9</t>
+          <t>-23,87; 64,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,26; -6,7</t>
+          <t>-63,64; -1,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 8,48</t>
+          <t>-2,34; 9,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,25</t>
+          <t>-5,63; 5,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,06</t>
+          <t>-8,99; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 7,88</t>
+          <t>-1,09; 8,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,61</t>
+          <t>-2,35; 7,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 8,89</t>
+          <t>-1,25; 8,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,75</t>
+          <t>-0,58; 6,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,64</t>
+          <t>-2,6; 4,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,42</t>
+          <t>-3,93; 3,61</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 98,19</t>
+          <t>-18,62; 114,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 63,43</t>
+          <t>-40,88; 62,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 16,11</t>
+          <t>-64,87; 9,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 141,6</t>
+          <t>-11,6; 146,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 120,05</t>
+          <t>-25,26; 121,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 148,88</t>
+          <t>-18,08; 147,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 82,66</t>
+          <t>-5,45; 88,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 60,0</t>
+          <t>-23,56; 56,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 41,9</t>
+          <t>-34,49; 46,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,46</t>
+          <t>-3,89; 1,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,3</t>
+          <t>-5,03; 0,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,12</t>
+          <t>-5,42; 0,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,03</t>
+          <t>-0,95; 4,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,26</t>
+          <t>-2,63; 2,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,22</t>
+          <t>-1,55; 4,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,11</t>
+          <t>-1,71; 2,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,66</t>
+          <t>-2,89; 0,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,4</t>
+          <t>-2,42; 1,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 14,37</t>
+          <t>-29,57; 13,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 3,48</t>
+          <t>-38,31; 3,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 1,04</t>
+          <t>-40,96; 1,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 47,33</t>
+          <t>-9,37; 48,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 27,52</t>
+          <t>-24,73; 26,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 49,2</t>
+          <t>-14,46; 47,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 21,92</t>
+          <t>-15,15; 22,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 7,18</t>
+          <t>-25,35; 7,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 14,29</t>
+          <t>-21,33; 16,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 5,8</t>
+          <t>-7,1; 5,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -0,0</t>
+          <t>-11,53; -0,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,85</t>
+          <t>-6,67; 6,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 7,62</t>
+          <t>-3,54; 7,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 4,13</t>
+          <t>-7,01; 3,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 11,55</t>
+          <t>-2,8; 11,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,8</t>
+          <t>-3,93; 4,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,31</t>
+          <t>-7,55; 0,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 7,65</t>
+          <t>-2,65; 7,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 63,58</t>
+          <t>-47,12; 65,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,42; 9,19</t>
+          <t>-79,13; 2,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 75,86</t>
+          <t>-41,68; 78,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 102,26</t>
+          <t>-31,88; 104,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 63,93</t>
+          <t>-57,32; 55,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 162,6</t>
+          <t>-27,92; 152,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 58,33</t>
+          <t>-30,06; 59,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 4,2</t>
+          <t>-59,47; 2,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 92,69</t>
+          <t>-22,25; 88,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -1,18</t>
+          <t>-10,54; -1,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -0,93</t>
+          <t>-10,86; -0,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,93</t>
+          <t>-7,91; 3,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,22</t>
+          <t>-2,89; 6,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,91</t>
+          <t>-6,53; 2,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,02</t>
+          <t>-2,28; 8,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,35</t>
+          <t>-5,75; 1,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; -0,21</t>
+          <t>-6,89; -0,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,15</t>
+          <t>-3,26; 4,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,19; -7,96</t>
+          <t>-64,46; -9,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,71; -5,23</t>
+          <t>-63,84; -2,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 26,52</t>
+          <t>-47,91; 27,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 81,51</t>
+          <t>-23,89; 85,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 35,76</t>
+          <t>-51,19; 34,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 107,34</t>
+          <t>-20,71; 106,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 12,61</t>
+          <t>-39,66; 16,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -2,02</t>
+          <t>-49,69; -4,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 41,93</t>
+          <t>-23,8; 42,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,27</t>
+          <t>-5,75; 4,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 9,4</t>
+          <t>-1,98; 8,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 2,28</t>
+          <t>-7,03; 2,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 3,52</t>
+          <t>-6,6; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 5,03</t>
+          <t>-6,2; 5,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -0,44</t>
+          <t>-10,04; -0,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,32</t>
+          <t>-4,75; 2,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 5,13</t>
+          <t>-2,46; 5,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,19</t>
+          <t>-7,33; -0,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 69,74</t>
+          <t>-51,97; 74,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 154,42</t>
+          <t>-19,55; 125,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 44,2</t>
+          <t>-65,01; 38,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 47,75</t>
+          <t>-49,2; 57,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 66,04</t>
+          <t>-44,95; 65,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,69; -0,47</t>
+          <t>-74,28; 0,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 31,74</t>
+          <t>-39,81; 34,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 64,89</t>
+          <t>-20,99; 67,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,64; -1,03</t>
+          <t>-63,39; -2,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,39</t>
+          <t>-2,52; 8,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 5,26</t>
+          <t>-5,69; 4,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 0,65</t>
+          <t>-8,29; 1,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,04</t>
+          <t>-1,7; 7,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 7,13</t>
+          <t>-1,95; 6,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 8,72</t>
+          <t>-0,78; 9,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,89</t>
+          <t>-0,63; 6,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,58</t>
+          <t>-2,33; 4,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,61</t>
+          <t>-3,92; 3,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 114,42</t>
+          <t>-18,48; 93,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 62,7</t>
+          <t>-41,62; 59,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 9,55</t>
+          <t>-61,74; 21,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 146,22</t>
+          <t>-19,23; 138,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 121,39</t>
+          <t>-21,18; 122,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 147,85</t>
+          <t>-11,76; 158,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 88,5</t>
+          <t>-6,28; 81,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 56,07</t>
+          <t>-22,06; 59,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 46,01</t>
+          <t>-34,27; 43,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,39</t>
+          <t>-3,71; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,35</t>
+          <t>-5,14; 0,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,13</t>
+          <t>-5,2; 0,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,03</t>
+          <t>-1,0; 4,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,27</t>
+          <t>-2,79; 2,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,02</t>
+          <t>-1,51; 4,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,16</t>
+          <t>-1,65; 2,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,72</t>
+          <t>-3,1; 0,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,6</t>
+          <t>-2,43; 1,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 13,56</t>
+          <t>-29,2; 15,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 3,7</t>
+          <t>-39,1; 4,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 1,95</t>
+          <t>-41,57; 2,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 48,77</t>
+          <t>-9,46; 54,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 26,08</t>
+          <t>-25,32; 30,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 47,72</t>
+          <t>-14,51; 50,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 22,32</t>
+          <t>-14,4; 21,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 7,38</t>
+          <t>-26,79; 6,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 16,89</t>
+          <t>-21,09; 16,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,61</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,86</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-5,87</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,84</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,76</t>
+          <t>-3,87; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -0,23</t>
+          <t>-6,3; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 6,58</t>
+          <t>-1,01; 14,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 7,05</t>
+          <t>-6,96; 5,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,87</t>
+          <t>-11,23; 0,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 11,48</t>
+          <t>-6,2; 6,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,89</t>
+          <t>-3,82; 4,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,18</t>
+          <t>-7,22; 0,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 7,64</t>
+          <t>-2,23; 7,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-13,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-7,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-49,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-13,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>-0,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 65,7</t>
+          <t>-32,86; 118,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 2,06</t>
+          <t>-54,7; 68,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 78,37</t>
+          <t>-10,12; 192,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 104,21</t>
+          <t>-47,22; 71,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 55,83</t>
+          <t>-74,59; 10,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 152,75</t>
+          <t>-41,84; 72,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 59,07</t>
+          <t>-29,95; 55,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 2,45</t>
+          <t>-55,51; 6,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 88,5</t>
+          <t>-18,49; 87,45</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,62</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-5,86</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -1,15</t>
+          <t>-2,77; 6,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -0,48</t>
+          <t>-5,97; 3,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 3,21</t>
+          <t>-2,43; 7,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 6,63</t>
+          <t>-11,14; -0,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 2,51</t>
+          <t>-10,75; -0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 8,22</t>
+          <t>-7,66; 4,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,55</t>
+          <t>-5,35; 1,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -0,49</t>
+          <t>-6,82; -0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,18</t>
+          <t>-3,17; 4,31</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-15,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-42,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-41,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-17,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-15,85%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>-13,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,46; -9,89</t>
+          <t>-23,36; 85,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,84; -2,79</t>
+          <t>-46,98; 42,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 27,86</t>
+          <t>-18,51; 96,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 85,25</t>
+          <t>-63,77; -5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 34,41</t>
+          <t>-64,25; -0,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 106,42</t>
+          <t>-45,37; 33,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 16,36</t>
+          <t>-39,07; 13,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,69; -4,81</t>
+          <t>-48,91; -1,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 42,1</t>
+          <t>-23,06; 40,96</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,42</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,52</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,43</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,36</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,53</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,94</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,78</t>
+          <t>-2,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 4,31</t>
+          <t>-6,88; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 8,23</t>
+          <t>-6,42; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 2,21</t>
+          <t>-9,26; 1,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,15</t>
+          <t>-5,53; 4,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,2</t>
+          <t>-1,85; 8,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -0,1</t>
+          <t>-6,15; 3,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,55</t>
+          <t>-4,68; 2,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,3</t>
+          <t>-2,23; 5,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,26</t>
+          <t>-6,71; 0,5</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-13,3%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-4,91%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-41,52%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-8,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>39,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-29,82%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-13,3%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-4,91%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-46,38%</t>
+          <t>-14,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-39,3%</t>
+          <t>-30,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 74,26</t>
+          <t>-50,86; 50,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 125,43</t>
+          <t>-46,5; 79,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,01; 38,78</t>
+          <t>-70,61; 19,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 57,86</t>
+          <t>-51,12; 75,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,95; 65,46</t>
+          <t>-16,69; 150,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 0,81</t>
+          <t>-55,71; 70,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,81; 34,67</t>
+          <t>-40,41; 35,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 67,99</t>
+          <t>-20,94; 73,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,39; -2,94</t>
+          <t>-57,77; 8,32</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,95</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,11</t>
+          <t>-1,46; 7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,8</t>
+          <t>-2,29; 6,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,62</t>
+          <t>-1,39; 9,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,88</t>
+          <t>-2,93; 8,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,77</t>
+          <t>-5,28; 5,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 9,16</t>
+          <t>-8,78; 1,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,67</t>
+          <t>-0,71; 6,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,56</t>
+          <t>-2,85; 4,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,46</t>
+          <t>-3,94; 3,62</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38,59%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>26,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-2,7%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-35,58%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>38,59%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>-31,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 93,41</t>
+          <t>-15,54; 141,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 59,18</t>
+          <t>-24,33; 120,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 21,15</t>
+          <t>-16,58; 154,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 138,52</t>
+          <t>-21,88; 98,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 122,26</t>
+          <t>-39,56; 63,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 158,92</t>
+          <t>-62,7; 21,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 81,17</t>
+          <t>-7,79; 82,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 59,1</t>
+          <t>-24,31; 60,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 43,5</t>
+          <t>-33,89; 45,05</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,22</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,52</t>
+          <t>-0,86; 4,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,45</t>
+          <t>-2,58; 2,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,31</t>
+          <t>-0,96; 4,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,33</t>
+          <t>-3,92; 1,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,5</t>
+          <t>-4,95; 0,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,2</t>
+          <t>-4,38; 0,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,05</t>
+          <t>-1,77; 2,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,6</t>
+          <t>-3,12; 0,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,61</t>
+          <t>-1,78; 2,0</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,47%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-10,45%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-19,08%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-22,62%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,47%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>-16,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,78%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 15,52</t>
+          <t>-9,16; 47,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 4,48</t>
+          <t>-25,15; 27,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 2,82</t>
+          <t>-8,54; 55,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 54,61</t>
+          <t>-30,1; 14,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 30,91</t>
+          <t>-38,25; 3,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 50,73</t>
+          <t>-34,64; 9,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 21,31</t>
+          <t>-15,13; 21,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 6,39</t>
+          <t>-26,87; 7,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 16,77</t>
+          <t>-15,68; 20,62</t>
         </is>
       </c>
     </row>
